--- a/numerical-workflows/v2/framework/06_最终配置/爬塔/00_配置清单.xlsx
+++ b/numerical-workflows/v2/framework/06_最终配置/爬塔/00_配置清单.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="配置清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置清单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,11 +468,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>223</v>
+        <v>451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VALUE_READY_FIRST_AND_IDLE_CHG042</t>
+          <t>VALUE_READY_FIRST_AND_IDLE_20260920</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>首通100包218行（含1074×4000）；挂机24003001共5行；常规/赛季包停用。</t>
+          <t>2026-09-20扩展101-200层：新增首通包24000101-24000200共221行(平推第100层面额：小层1074x50/元晶50、尾5层1074x180/旅券6、尾0层1074x280/熔晶1/元晶600；120/140/160/180/200层1156x40+1157x3、130/160/200层3027x300)。1-100层CHG-044口径不变。</t>
         </is>
       </c>
     </row>
@@ -498,11 +498,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VALUE_READY_FIRST_ONLY_CHG042</t>
+          <t>VALUE_READY_500L_20260920</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>写首通引用/预览（每层含1074）；清空Reward/FallRewardDrop。</t>
+          <t>2026-09-20扩展：新增第五包体300401-300500共100行(T=24000101-24000200、I=包内层1-100、名=前缀段+侵入N级、LevelType_PVP、Unlimited、S=BLT_Main)；既有400行不变。</t>
         </is>
       </c>
     </row>
@@ -528,11 +528,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VALUE_READY_REFERENCE_CHG041</t>
+          <t>VALUE_READY_200L_20260920</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1-100层引用首通DropId；尾数5层展示106，整10层展示103。</t>
+          <t>2026-09-20扩展：新增Layer101-200引用24000101-24000200；尾5层展示106、尾0层展示103、其余留空。</t>
         </is>
       </c>
     </row>
@@ -588,11 +588,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VALUE_READY_100_LAYERS_CHG037</t>
+          <t>VALUE_READY_200L_20260920</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>金币/零件逐层增长；材料30层起每10层提升、100层60/日。</t>
+          <t>2026-09-20扩展：101-200层挂机金币每层+400(封顶230,000)、零件每5层+1(封顶270)、材料每10层+2(封顶80)；1-100层不变。</t>
         </is>
       </c>
     </row>
